--- a/backend/data/donglin/agent_demo/CSG_walkthrough_filled.xlsx
+++ b/backend/data/donglin/agent_demo/CSG_walkthrough_filled.xlsx
@@ -2226,7 +2226,7 @@
     <row r="2">
       <c r="A2" s="223" t="inlineStr">
         <is>
-          <t>公司：中国南玻集团股份有限公司</t>
+          <t>公司：乙公司（光伏玻璃）</t>
         </is>
       </c>
     </row>
@@ -6161,8 +6161,8 @@
     <mergeCell ref="R26:R30"/>
     <mergeCell ref="J26:J30"/>
     <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="AM4:AM6"/>
     <mergeCell ref="T26:T30"/>
-    <mergeCell ref="AM4:AM6"/>
     <mergeCell ref="L26:L30"/>
     <mergeCell ref="L16:L21"/>
     <mergeCell ref="AT16:AT21"/>
@@ -6178,8 +6178,8 @@
     <mergeCell ref="AP22:AP25"/>
     <mergeCell ref="I16:I21"/>
     <mergeCell ref="AF7:AF15"/>
+    <mergeCell ref="AF16:AF21"/>
     <mergeCell ref="K7:K15"/>
-    <mergeCell ref="AF16:AF21"/>
     <mergeCell ref="AH7:AH15"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="S26:S30"/>
